--- a/artfynd/A 7229-2022 artfynd.xlsx
+++ b/artfynd/A 7229-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7229-2022 artfynd.xlsx
+++ b/artfynd/A 7229-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91452740</v>
+        <v>91452610</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567244.1325910557</v>
+        <v>567217</v>
       </c>
       <c r="R2" t="n">
-        <v>6866770.033469033</v>
+        <v>6866726</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-09-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,55 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91452862</v>
+        <v>91452611</v>
       </c>
       <c r="B3" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lusseås, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567265.8919619104</v>
+        <v>567243</v>
       </c>
       <c r="R3" t="n">
-        <v>6866743.142077202</v>
+        <v>6866679</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +840,9 @@
           <t>2020-09-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91452621</v>
+        <v>91452642</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567155.8046624908</v>
+        <v>567160</v>
       </c>
       <c r="R4" t="n">
-        <v>6866727.781929085</v>
+        <v>6866728</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,19 +937,9 @@
           <t>2020-09-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91452610</v>
+        <v>91452621</v>
       </c>
       <c r="B5" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567217.1645416087</v>
+        <v>567156</v>
       </c>
       <c r="R5" t="n">
-        <v>6866726.165103962</v>
+        <v>6866728</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,19 +1034,9 @@
           <t>2020-09-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91452642</v>
+        <v>91452869</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567160.0487975145</v>
+        <v>567078</v>
       </c>
       <c r="R6" t="n">
-        <v>6866727.865550771</v>
+        <v>6866718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,19 +1131,9 @@
           <t>2020-09-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-09-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,6 +1157,205 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>91452862</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lusseås, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>567266</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6866743</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-09-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-09-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>91452740</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lusseås, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>567244</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6866770</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-09-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-09-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
